--- a/Allgemeine Daten/covariate/flea_jumplength_bloodmeal_n21.xlsx
+++ b/Allgemeine Daten/covariate/flea_jumplength_bloodmeal_n21.xlsx
@@ -381,13 +381,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C2">
-        <v>5.5</v>
+        <v>13.1</v>
       </c>
       <c r="D2">
-        <v>28.2</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="3">
@@ -395,13 +395,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>10.5</v>
+        <v>1.2</v>
       </c>
       <c r="C3">
-        <v>13.4</v>
+        <v>4.4</v>
       </c>
       <c r="D3">
-        <v>35.1</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="4">
@@ -423,13 +423,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>10.2</v>
+        <v>3.5</v>
       </c>
       <c r="C5">
-        <v>15.2</v>
+        <v>6.7</v>
       </c>
       <c r="D5">
-        <v>30.1</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="6">
@@ -437,13 +437,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="C6">
-        <v>6.6</v>
+        <v>11.8</v>
       </c>
       <c r="D6">
-        <v>14.1</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="7">
@@ -451,13 +451,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>9.300000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="C7">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="D7">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="8">
@@ -465,13 +465,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="D8">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="9">
@@ -479,13 +479,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3.9</v>
+        <v>11.1</v>
       </c>
       <c r="C9">
-        <v>7.4</v>
+        <v>13.6</v>
       </c>
       <c r="D9">
-        <v>21.4</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="10">
@@ -493,13 +493,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="C10">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="D10">
-        <v>15.2</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="11">
@@ -507,13 +507,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="C11">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="D11">
-        <v>27.2</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="12">
@@ -521,13 +521,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="C12">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="D12">
-        <v>26.2</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="13">
@@ -535,13 +535,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>9.800000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="C13">
-        <v>13.1</v>
+        <v>11.5</v>
       </c>
       <c r="D13">
-        <v>32.4</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="14">
@@ -549,13 +549,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>11.5</v>
       </c>
       <c r="D14">
-        <v>29.2</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="15">
@@ -563,13 +563,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="C15">
-        <v>11.8</v>
+        <v>7.5</v>
       </c>
       <c r="D15">
-        <v>19.1</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="16">
@@ -577,13 +577,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="C16">
-        <v>14.4</v>
+        <v>13.4</v>
       </c>
       <c r="D16">
-        <v>27.6</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="17">
@@ -591,13 +591,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="C17">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="D17">
-        <v>21.6</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="18">
@@ -605,13 +605,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="C18">
-        <v>16.2</v>
+        <v>14.4</v>
       </c>
       <c r="D18">
-        <v>37.1</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="19">
@@ -619,13 +619,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>3.5</v>
+        <v>10.2</v>
       </c>
       <c r="C19">
-        <v>6.7</v>
+        <v>15.2</v>
       </c>
       <c r="D19">
-        <v>24.6</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="20">
@@ -633,13 +633,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>5.1</v>
+        <v>1.8</v>
       </c>
       <c r="C20">
-        <v>8.9</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>14.2</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="21">
@@ -661,13 +661,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="C22">
-        <v>13.6</v>
+        <v>16.2</v>
       </c>
       <c r="D22">
-        <v>33.3</v>
+        <v>37.1</v>
       </c>
     </row>
   </sheetData>

--- a/Allgemeine Daten/covariate/flea_jumplength_bloodmeal_n21.xlsx
+++ b/Allgemeine Daten/covariate/flea_jumplength_bloodmeal_n21.xlsx
@@ -362,17 +362,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>bloodmeal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>bodyweight</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>jumplength</t>
         </is>
       </c>
     </row>
@@ -380,294 +380,336 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>9.800000000000001</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C2">
-        <v>13.1</v>
+        <v>6.2</v>
       </c>
       <c r="D2">
-        <v>32.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1.2</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C3">
-        <v>4.4</v>
+        <v>10.2</v>
       </c>
       <c r="D3">
-        <v>27.2</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="C4">
         <v>7.1</v>
       </c>
-      <c r="C4">
-        <v>10.3</v>
-      </c>
       <c r="D4">
-        <v>14.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>3.5</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C5">
-        <v>6.7</v>
+        <v>10.5</v>
       </c>
       <c r="D5">
-        <v>24.6</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>7.6</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C6">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="D6">
-        <v>19.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3.9</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C7">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="D7">
-        <v>21.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>5.1</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C8">
-        <v>8.9</v>
+        <v>1.2</v>
       </c>
       <c r="D8">
-        <v>14.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>11.1</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C9">
-        <v>13.6</v>
+        <v>5.5</v>
       </c>
       <c r="D9">
-        <v>33.3</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>6.2</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C10">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="D10">
-        <v>14.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
-        <v>2.4</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C11">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D11">
-        <v>28.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
-        <v>3.1</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C12">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="D12">
-        <v>21.6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
-        <v>6.5</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C13">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
       <c r="D13">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>9.300000000000001</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C14">
-        <v>11.5</v>
+        <v>3.1</v>
       </c>
       <c r="D14">
-        <v>22.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15">
-        <v>5.5</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C15">
-        <v>7.5</v>
+        <v>11.8</v>
       </c>
       <c r="D15">
-        <v>13.1</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16">
-        <v>10.5</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C16">
-        <v>13.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D16">
-        <v>35.1</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17">
-        <v>2.8</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C17">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="D17">
-        <v>26.2</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>8.6</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C18">
-        <v>14.4</v>
+        <v>3.9</v>
       </c>
       <c r="D18">
-        <v>27.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19">
-        <v>10.2</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C19">
-        <v>15.2</v>
+        <v>2.4</v>
       </c>
       <c r="D19">
-        <v>30.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20">
-        <v>1.8</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D20">
-        <v>29.2</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>4.6</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C21">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="D21">
-        <v>15.2</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22">
-        <v>11.8</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
       <c r="C22">
-        <v>16.2</v>
+        <v>8.6</v>
       </c>
       <c r="D22">
-        <v>37.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Allgemeine Daten/covariate/flea_jumplength_bloodmeal_n21.xlsx
+++ b/Allgemeine Daten/covariate/flea_jumplength_bloodmeal_n21.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,6 +375,11 @@
           <t>bodyweight</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>jumplength</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -386,10 +391,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>6.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D2">
-        <v>9.6</v>
+        <v>14.5</v>
+      </c>
+      <c r="E2">
+        <v>22.2</v>
       </c>
     </row>
     <row r="3">
@@ -402,10 +410,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>10.2</v>
+        <v>6.5</v>
       </c>
       <c r="D3">
-        <v>12.8</v>
+        <v>9.9</v>
+      </c>
+      <c r="E3">
+        <v>15.2</v>
       </c>
     </row>
     <row r="4">
@@ -418,10 +429,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>7.1</v>
+        <v>3.1</v>
       </c>
       <c r="D4">
-        <v>6.6</v>
+        <v>3.4</v>
+      </c>
+      <c r="E4">
+        <v>21.6</v>
       </c>
     </row>
     <row r="5">
@@ -434,10 +448,13 @@
         </is>
       </c>
       <c r="C5">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="D5">
-        <v>11.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="E5">
+        <v>27.6</v>
       </c>
     </row>
     <row r="6">
@@ -450,10 +467,13 @@
         </is>
       </c>
       <c r="C6">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="D6">
-        <v>3.8</v>
+        <v>3.2</v>
+      </c>
+      <c r="E6">
+        <v>21.4</v>
       </c>
     </row>
     <row r="7">
@@ -466,10 +486,13 @@
         </is>
       </c>
       <c r="C7">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="D7">
-        <v>8.6</v>
+        <v>7.1</v>
+      </c>
+      <c r="E7">
+        <v>14.2</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +508,10 @@
         <v>1.2</v>
       </c>
       <c r="D8">
-        <v>4.3</v>
+        <v>3.8</v>
+      </c>
+      <c r="E8">
+        <v>24.1</v>
       </c>
     </row>
     <row r="9">
@@ -498,10 +524,13 @@
         </is>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="D9">
-        <v>8.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="E9">
+        <v>35.1</v>
       </c>
     </row>
     <row r="10">
@@ -514,10 +543,13 @@
         </is>
       </c>
       <c r="C10">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="D10">
-        <v>6.8</v>
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>24.6</v>
       </c>
     </row>
     <row r="11">
@@ -530,10 +562,13 @@
         </is>
       </c>
       <c r="C11">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D11">
-        <v>5.4</v>
+        <v>15.1</v>
+      </c>
+      <c r="E11">
+        <v>32.4</v>
       </c>
     </row>
     <row r="12">
@@ -546,10 +581,13 @@
         </is>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="D12">
-        <v>11.5</v>
+        <v>1.7</v>
+      </c>
+      <c r="E12">
+        <v>28.2</v>
       </c>
     </row>
     <row r="13">
@@ -562,10 +600,13 @@
         </is>
       </c>
       <c r="C13">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="D13">
-        <v>15.1</v>
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <v>29.8</v>
       </c>
     </row>
     <row r="14">
@@ -578,10 +619,13 @@
         </is>
       </c>
       <c r="C14">
-        <v>3.1</v>
+        <v>11.1</v>
       </c>
       <c r="D14">
-        <v>6.4</v>
+        <v>12.9</v>
+      </c>
+      <c r="E14">
+        <v>33.3</v>
       </c>
     </row>
     <row r="15">
@@ -594,10 +638,13 @@
         </is>
       </c>
       <c r="C15">
-        <v>11.8</v>
+        <v>4.6</v>
       </c>
       <c r="D15">
-        <v>17.2</v>
+        <v>7.8</v>
+      </c>
+      <c r="E15">
+        <v>15.2</v>
       </c>
     </row>
     <row r="16">
@@ -610,10 +657,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>9.300000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="D16">
-        <v>15.4</v>
+        <v>10.3</v>
+      </c>
+      <c r="E16">
+        <v>13.1</v>
       </c>
     </row>
     <row r="17">
@@ -626,10 +676,13 @@
         </is>
       </c>
       <c r="C17">
-        <v>7.6</v>
+        <v>2.8</v>
       </c>
       <c r="D17">
-        <v>10.8</v>
+        <v>4.9</v>
+      </c>
+      <c r="E17">
+        <v>26.2</v>
       </c>
     </row>
     <row r="18">
@@ -642,10 +695,13 @@
         </is>
       </c>
       <c r="C18">
-        <v>3.9</v>
+        <v>11.8</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>14.8</v>
+      </c>
+      <c r="E18">
+        <v>35.1</v>
       </c>
     </row>
     <row r="19">
@@ -658,10 +714,13 @@
         </is>
       </c>
       <c r="C19">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>5.6</v>
+      </c>
+      <c r="E19">
+        <v>14.1</v>
       </c>
     </row>
     <row r="20">
@@ -674,10 +733,13 @@
         </is>
       </c>
       <c r="C20">
-        <v>9.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="D20">
-        <v>11.4</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E20">
+        <v>14.3</v>
       </c>
     </row>
     <row r="21">
@@ -690,10 +752,13 @@
         </is>
       </c>
       <c r="C21">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="D21">
-        <v>8.300000000000001</v>
+        <v>11.5</v>
+      </c>
+      <c r="E21">
+        <v>19.1</v>
       </c>
     </row>
     <row r="22">
@@ -706,10 +771,13 @@
         </is>
       </c>
       <c r="C22">
-        <v>8.6</v>
+        <v>1.8</v>
       </c>
       <c r="D22">
-        <v>8.300000000000001</v>
+        <v>4.3</v>
+      </c>
+      <c r="E22">
+        <v>29.2</v>
       </c>
     </row>
   </sheetData>
